--- a/skills/claude-skills/extract-engine/examples/sample-workbook.xlsx
+++ b/skills/claude-skills/extract-engine/examples/sample-workbook.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -568,6 +568,16 @@
           <t>emit_concat_ws_line</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>line_ending</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>max_rows_per_file</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -578,6 +588,14 @@
       </c>
       <c r="C2" t="n">
         <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CRLF</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1000000</v>
       </c>
     </row>
   </sheetData>
